--- a/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>7882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12125</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10010</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>9548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18607</t>
+          <t>18580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>25130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37061</t>
+          <t>36768</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54085</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2654</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10157</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>6371</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>10890</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4401</t>
+          <t>4302</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>11849</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,45%</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>8924</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1685</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>6673</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>872</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13192</t>
+          <t>13493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>23245</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31397</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46476</t>
+          <t>46289</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,53%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10188</t>
+          <t>9784</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9636</t>
+          <t>9700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21932</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,76%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1378</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2659</t>
+          <t>2606</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10067</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3217</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>380</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>8786</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7061</t>
+          <t>7068</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4328</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14239</t>
+          <t>13932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>10492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,33%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11993</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21256</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29476</t>
+          <t>29471</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>793</t>
+          <t>849</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6998</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>776</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7646</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11795</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9162</t>
+          <t>9079</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12302</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>27,79%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2555</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>15137</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8075</t>
+          <t>8223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23894</t>
+          <t>23748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>22644</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>74916</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17543</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31872</t>
+          <t>32364</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>47190</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>111591</t>
+          <t>112580</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,74%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>14878</t>
+          <t>15327</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49322</t>
+          <t>49784</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>21253</t>
+          <t>20411</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35347</t>
+          <t>35748</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36718</t>
+          <t>36480</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>78077</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,2%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10255</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6552</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16773</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8396</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13693</t>
+          <t>13929</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3358</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11954</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22975</t>
+          <t>22383</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1508</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8482</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11996</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11883</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>24210</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16315</t>
+          <t>16669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30070</t>
+          <t>29893</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3641,12 +3641,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31199</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>49876</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3656,12 +3656,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25027</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22897</t>
+          <t>23148</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38851</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>17904</t>
+          <t>18718</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>9825</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6747</t>
+          <t>6426</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>18407</t>
+          <t>17237</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>7514</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4631</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9858</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>8925</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19436</t>
+          <t>19092</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12803</t>
+          <t>13025</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,85%</t>
+          <t>45,53%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>10944</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3958</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9099</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20292</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,3%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>777</t>
+          <t>850</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10833</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14223</t>
+          <t>14515</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,49%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3686</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>10902</t>
+          <t>10877</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>927</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6032</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>17382</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>11818</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27946</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13296</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>28041</t>
+          <t>27280</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28034</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>51058</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>53137</t>
+          <t>54092</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>128766</t>
+          <t>127191</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57185</t>
+          <t>57044</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83997</t>
+          <t>83725</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>120430</t>
+          <t>120423</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>208105</t>
+          <t>216808</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>40,31%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>65254</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>109246</t>
+          <t>109470</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>108529</t>
+          <t>106978</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>140413</t>
+          <t>137314</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>181144</t>
+          <t>179041</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>238967</t>
+          <t>237978</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>44,25%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>20332</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>40221</t>
+          <t>41321</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>33738</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>55494</t>
+          <t>55701</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>57616</t>
+          <t>58055</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>89941</t>
+          <t>91228</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>22134</t>
+          <t>22615</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>44418</t>
+          <t>44341</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20645</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38698</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>49181</t>
+          <t>50312</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>76498</t>
+          <t>77533</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/RUIDO_2-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7882</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1368</t>
+          <t>1457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6872</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>6652</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2488</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2426</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1831</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9228</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28522</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21693</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>34188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>61,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>46,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>73,48%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>14208</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9548</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18580</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>42,28%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>28,42%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>55,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>45461</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36768</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>49763</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>62,19%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10818</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5908</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18249</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,7%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2733</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9929</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,55%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>10587</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6371</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>10603</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16214</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10890</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24482</t>
+          <t>23345</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1875</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5876</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,63%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7642</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4302</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11849</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,26%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>9765</t>
+          <t>9361</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5760</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>15011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>46530</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>46530</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46530</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33601</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83398</t>
+          <t>80016</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3563</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9362</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>9,98%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>26,22%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3430</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2998</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3679</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1174</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8924</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>9,85%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4330</t>
+          <t>4206</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1592</t>
+          <t>1629</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2608</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>732</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6635</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2,05%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18,59%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1554</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6673</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>1605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7084</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>6368</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>19727</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14268</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>24979</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>55,26%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>39,97%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>69,97%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18511</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13493</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>23245</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>50,45%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>36,77%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>63,35%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>18499</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25375</t>
+          <t>23552</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>67,96%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>38860</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>30619</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>44729</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4891</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2051</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9839</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,74%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>27,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>10276</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6313</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15342</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>28,01%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,21%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>10444</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>6345</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22029</t>
+          <t>22076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>30,35%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9137</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>25,59%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>3641</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1384</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8119</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,77%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>3890</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>1341</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10119</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9333</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5150</t>
+          <t>5231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14837</t>
+          <t>14971</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>35700</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>35700</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>35700</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>36691</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>36691</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>36691</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37337</t>
+          <t>37035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>74028</t>
+          <t>72734</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2875</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,96%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3287</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>309</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4117</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4934</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1791</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>8459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>12236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>13962</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>9801</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17742</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>73,45%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>6570</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>3544</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10492</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>36,75%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>19,82%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>58,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11277</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21331</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23187</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>14939</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29471</t>
+          <t>26071</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>62,58%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3137</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>921</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11381</t>
+          <t>12058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>28,94%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3357</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1260</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>6806</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>13,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>28,17%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6191</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>15,25%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>34,63%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>2831</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1562</t>
+          <t>897</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9079</t>
+          <t>6763</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3964</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>10817</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -2649,57 +2649,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>24156</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>17879</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>5817</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15137</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>7996</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>13936</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>13813</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8223</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23748</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>21417</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>15516</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>28574</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>30,47%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>22,08%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>40,66%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>46310</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>22644</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>74916</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>46,23%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>74,79%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>20034</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32364</t>
+          <t>28709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>70376</t>
+          <t>41451</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>32920</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>112580</t>
+          <t>54194</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>25899</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>18893</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>32496</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>36,85%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>26,88%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>46,24%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>33285</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>15327</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>49784</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>33,23%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>49,7%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>28014</t>
+          <t>31198</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>24542</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>35748</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>61299</t>
+          <t>57096</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>36480</t>
+          <t>47431</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>78077</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>10466</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>6196</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>16843</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>14,89%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>8,82%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,96%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>4944</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1671</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>10403</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>10,39%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10856</t>
+          <t>4831</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>2177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17187</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>15799</t>
+          <t>15298</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6684</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12738</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>9,51%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>7642</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>3120</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>13929</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>13,91%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6597</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3498</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12633</t>
+          <t>11278</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>14488</t>
+          <t>13281</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7531</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>19862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>14,09%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>70283</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>70283</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>70283</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>100171</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>76465</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3680</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7770</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2,39%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>2382</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>5866</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>14,33%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>829</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6241</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2730</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>11743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20328</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>14383</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>26864</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>36,05%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>47,64%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>17252</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>12228</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>24210</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>29,87%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>59,15%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>14003</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>16669</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29893</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>39902</t>
+          <t>34331</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31199</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>49876</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>17665</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>12433</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>24446</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>31,32%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>22,05%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>43,35%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>12428</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>7935</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>17670</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>30,36%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>19,39%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18439</t>
+          <t>12327</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12524</t>
+          <t>7983</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25027</t>
+          <t>17135</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23012</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>40,59%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>8594</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>14634</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>15,24%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>25,95%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>3624</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>1349</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>7222</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>8,85%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>17,64%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13648</t>
+          <t>7056</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6659</t>
+          <t>7147</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>18718</t>
+          <t>18236</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>19,36%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>6126</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>11437</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>5246</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>2269</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>9489</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>23,18%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2504</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11171</t>
+          <t>9559</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>17237</t>
+          <t>18241</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,37%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>56394</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>56394</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>56394</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>40933</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>40933</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>40933</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>59461</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>94170</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>94170</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>94170</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4130,72 +4130,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>988</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>4142</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>14,06%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>3364</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>7567</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>13,64%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>965</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4848</t>
+          <t>8470</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>11151</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,29%</t>
         </is>
       </c>
     </row>
@@ -4243,72 +4243,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10957</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>6778</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>16179</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>37,2%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>54,93%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>4856</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>19,68%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>35,46%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>5043</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>2484</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19092</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>22762</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -4356,72 +4356,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>7653</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>4081</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>12381</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>13,86%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>42,03%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>6615</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>10944</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>26,81%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>44,36%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>7825</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>20005</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,41%</t>
         </is>
       </c>
     </row>
@@ -4469,72 +4469,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>5581</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2139</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>10143</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>34,43%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>3026</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>850</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>6487</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>7429</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>3,45%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>5454</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2469</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>10956</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>7,65%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>8480</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14515</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -4582,72 +4582,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>1136</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>9578</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>14,51%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>32,52%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>6808</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>10877</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>44,09%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>7275</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>12355</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>10923</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>17382</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25492</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54947</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4812,72 +4812,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>17840</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>25045</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>6,8%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>4,66%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>9,54%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>18535</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>11438</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>27946</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>4,5%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12742</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>27280</t>
+          <t>28357</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>38331</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>27807</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>51058</t>
+          <t>49672</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -4925,72 +4925,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>60590</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>50229</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>74158</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>23,08%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>28,25%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>79452</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>54092</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>127191</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>31,29%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>21,3%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>50,09%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>69116</t>
+          <t>49375</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>57044</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>83725</t>
+          <t>60567</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>148568</t>
+          <t>109965</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>120423</t>
+          <t>95011</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>216808</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -5038,72 +5038,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>113428</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>98996</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>126924</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>43,21%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>37,71%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>48,35%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>91617</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>65254</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>109470</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>36,08%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>25,7%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>43,11%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>122497</t>
+          <t>88917</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>106978</t>
+          <t>76468</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>137314</t>
+          <t>100254</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>48,37%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>214114</t>
+          <t>202345</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>179041</t>
+          <t>181925</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>237978</t>
+          <t>221758</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -5151,72 +5151,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>43433</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>33291</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>55764</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>12,68%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>21,24%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>30634</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>20148</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>41321</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>12,06%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>43201</t>
+          <t>30917</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>32903</t>
+          <t>23720</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>55701</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>73835</t>
+          <t>74350</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>61362</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>91228</t>
+          <t>89482</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -5264,72 +5264,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>27227</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>20311</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>37403</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>7,74%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>14,25%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>33707</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>22615</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>44341</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>13,27%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>17,46%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>29276</t>
+          <t>33514</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>20645</t>
+          <t>25106</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>43466</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>62982</t>
+          <t>60742</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>50312</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>75504</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,59%</t>
         </is>
       </c>
     </row>
@@ -5377,57 +5377,57 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>262518</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>262518</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>262518</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>347</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>253945</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>253945</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>253945</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>376</t>
-        </is>
-      </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>283886</t>
+          <t>221948</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>283886</t>
+          <t>221948</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>283886</t>
+          <t>221948</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>537830</t>
+          <t>484466</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>537830</t>
+          <t>484466</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>537830</t>
+          <t>484466</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
